--- a/paper/source_data/ed1_source_data.xlsx
+++ b/paper/source_data/ed1_source_data.xlsx
@@ -495,9 +495,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>**Extended Data Fig. 1 | One BRAN state, many uses, each beside its strongest comparator.**
-**a**, Lines give BRAN, the strongest or prespecified primary comparator, and BRAN minus comparator with its paired 95% interval on an axis symmetric about zero (half-range at right, right favours BRAN). Intervals are from participant, admission or survey-cluster bootstrap, or the survey design for NHANES models. BRAN tied in 12 and trailed in 9 of 21 comparisons with the strongest comparator and led in none. Retrieval led raw CCA only before age adjustment (Fig. 2a). On the official test the development referral gain did not replicate. Hazard ratios (HR) and betas are per SD, except top-fifth and cluster lines (members against non-members), and beside terms come from joint models. A retinal-route retrain changed eye-alone AUROC by −0.0051 [−0.0089, −0.0015] and was not adopted. KNHANES 2022 to 2023 raw analogs lay further from zero than BRAN distance for visual acuity and phase angle (Source Data). Retained-model retrieval, the NHANES outcome-trained flexible ceiling and Phenotypic Age in 1999 to 2004 are PLACEHOLDER. † Earlier checkpoint. CCA, canonical correlation analysis. pp, percentage points. Counts given as at least are rounded down to 20, other counts are exact.
-**b**, The predecessor model on the official test (352 people), normalized loss by arm (left), single arm minus paired (middle) and by target without intervals (right). Intervals are 95% from 2,000 patient-cluster bootstrap draws, and P values are one-sided and Holm-adjusted. Paired input was not shown better than the blood arm (P = 0.055), so the predecessor model's primary end point was not met. MoCA, Montreal Cognitive Assessment. MLCS, PLCS, VIA M and VIA P, AI-READI visual function scores.</t>
+          <t>**Extended Data Fig. 1 | One BRAN state, many uses, each beside its strongest comparator.** **a**, Lines give BRAN, the strongest or prespecified primary comparator and their paired difference (95% interval, symmetric axis, half-range at right). Intervals, participant, admission or survey-cluster bootstrap, or NHANES survey design. Against the strongest comparator BRAN tied 12, trailed 9 and led none of 21 paired comparisons. Retrieval led raw CCA only before age adjustment (Fig. 2a). The development referral gain did not replicate on the official test. Hazard ratios (HR) and betas are per SD, except top-fifth and cluster lines (members against non-members), and beside terms are from joint models. A retinal-route retrain changed eye-alone AUROC by −0.0051 [−0.0089, −0.0015] and was not adopted. KNHANES 2022 to 2023 raw analogs lay further from zero than BRAN distance for visual acuity and phase angle (Source Data). Retained-model retrieval, the NHANES outcome-trained flexible ceiling and Phenotypic Age in 1999 to 2004 are PLACEHOLDER. † Earlier checkpoint. CCA, canonical correlation analysis. pp, percentage points. Counts given as at least are floored to 20, others exact. **b**, Predecessor model, official test (352 people), normalized loss by arm (left), single arm minus paired (middle) and by target without intervals (right), with 95% intervals from 2,000 patient-cluster bootstrap draws and one-sided Holm-adjusted *P*. Paired input was not shown better than the blood arm (*P* = 0.055), so the primary end point was not met. MoCA, Montreal Cognitive Assessment. MLCS and PLCS, mesopic and photopic log contrast sensitivity. VIA M and VIA P, mesopic and photopic visual acuity.</t>
         </is>
       </c>
     </row>
